--- a/dcf/CRM.xlsx
+++ b/dcf/CRM.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1155,25 +1155,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.07551981193177065</v>
+        <v>0.07562807792947593</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.08051981193177066</v>
+        <v>0.08062807792947593</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.08551981193177065</v>
+        <v>0.08562807792947592</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.09051981193177065</v>
+        <v>0.09062807792947593</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.09551981193177066</v>
+        <v>0.09562807792947593</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.1005198119317706</v>
+        <v>0.1006280779294759</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.1055198119317707</v>
+        <v>0.1056280779294759</v>
       </c>
     </row>
     <row r="5">
@@ -1181,25 +1181,25 @@
         <v>12</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>244.1694352482385</v>
+        <v>243.9633515156189</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>234.8702819122594</v>
+        <v>234.6737745538454</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>226.0020024877249</v>
+        <v>225.8145724362829</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>217.5421982449278</v>
+        <v>217.3633748735834</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>209.4697439054773</v>
+        <v>209.2990832776169</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>201.764709456718</v>
+        <v>201.6017926912478</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>194.4082871081079</v>
+        <v>194.2527188519638</v>
       </c>
     </row>
     <row r="6">
@@ -1207,25 +1207,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>257.3204362832811</v>
+        <v>257.1011215691661</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>247.425250116552</v>
+        <v>247.2161698523821</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>237.9905182404612</v>
+        <v>237.791137813746</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>228.9922476464613</v>
+        <v>228.8020629556489</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>220.407811446265</v>
+        <v>220.2263470213313</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>212.2158649113581</v>
+        <v>212.0426721583692</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>204.3962670383428</v>
+        <v>204.2309225992708</v>
       </c>
     </row>
     <row r="7">
@@ -1233,25 +1233,25 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>270.4714373183238</v>
+        <v>270.2388916227135</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>259.9802183208445</v>
+        <v>259.7585651509187</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>249.9790339931975</v>
+        <v>249.7677031912091</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>240.4422970479949</v>
+        <v>240.2407510377143</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>231.3458789870526</v>
+        <v>231.1536107650458</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>222.6670203659983</v>
+        <v>222.4835516254905</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>214.3842469685777</v>
+        <v>214.2091263465778</v>
       </c>
     </row>
     <row r="8">
@@ -1259,25 +1259,25 @@
         <v>15</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>283.6224383533664</v>
+        <v>283.3766616762608</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>272.535186525137</v>
+        <v>272.3009604494554</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>261.9675497459338</v>
+        <v>261.7442685686722</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>251.8923464495284</v>
+        <v>251.6794391197798</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>242.2839465278403</v>
+        <v>242.0808745087602</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>233.1181758206384</v>
+        <v>232.924431092612</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>224.3722268988127</v>
+        <v>224.1873300938848</v>
       </c>
     </row>
     <row r="9">
@@ -1285,25 +1285,25 @@
         <v>16</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>296.7734393884091</v>
+        <v>296.5144317298082</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>285.0901547294296</v>
+        <v>284.8433557479922</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>273.9560654986701</v>
+        <v>273.7208339461353</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>263.3423958510621</v>
+        <v>263.1181272018453</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>253.2220140686279</v>
+        <v>253.0081382524746</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>243.5693312752786</v>
+        <v>243.3653105597334</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>234.3602068290476</v>
+        <v>234.1655338411918</v>
       </c>
     </row>
     <row r="10">
@@ -1311,25 +1311,25 @@
         <v>17</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>309.9244404234517</v>
+        <v>309.6522017833556</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>297.6451229337221</v>
+        <v>297.3857510465288</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>285.9445812514065</v>
+        <v>285.6973993235984</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>274.7924452525956</v>
+        <v>274.5568152839107</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>264.1600816094156</v>
+        <v>263.9354019961891</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>254.0204867299187</v>
+        <v>253.8061900268548</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>244.3481867592825</v>
+        <v>244.1437375884988</v>
       </c>
     </row>
     <row r="11">
@@ -1337,25 +1337,25 @@
         <v>18</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>323.0754414584944</v>
+        <v>322.7899718369029</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>310.2000911380147</v>
+        <v>309.9281463450656</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>297.9330970041428</v>
+        <v>297.6739647010615</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>286.2424946541292</v>
+        <v>285.9955033659762</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>275.0981491502033</v>
+        <v>274.8626657399034</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>264.4716421845589</v>
+        <v>264.2470694939761</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>254.3361666895174</v>
+        <v>254.1219413358058</v>
       </c>
     </row>
     <row r="13">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B13" s="55" t="n">
-        <v>166.1100006103516</v>
+        <v>171.3999938964844</v>
       </c>
     </row>
     <row r="14">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.09051981193177065</v>
+        <v>0.09062807792947593</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>15</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.8818956762867788</v>
+        <v>0.8818985932433789</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>166.1100006103516</v>
+        <v>171.3999938964844</v>
       </c>
     </row>
     <row r="49">
@@ -24702,13 +24702,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>251.8923464495284</v>
+        <v>251.6794391197798</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>344.4698137253017</v>
+        <v>344.1711124474268</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>182.2831163411123</v>
+        <v>182.1339396072948</v>
       </c>
     </row>
     <row r="59">
